--- a/data/trans_camb/P43-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43-Edad-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,33</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,31; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,2; 3,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,27; 8,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,78</t>
+          <t>-2,31; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,01</t>
+          <t>-3,2; 3,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 7,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 3,78</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 3,01</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 7,55</t>
+          <t>-2,27; 8,2</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>40,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,22%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40,52%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-33,95; 91,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-45,64; 69,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-38,41; 175,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 84,29</t>
+          <t>-33,95; 91,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 70,45</t>
+          <t>-45,64; 69,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 165,12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-39,96; 84,29</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-46,85; 70,45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-34,59; 165,12</t>
+          <t>-38,41; 175,53</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,08</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,78; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,38; 4,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,33; 5,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,7</t>
+          <t>-3,78; 3,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,36</t>
+          <t>-3,38; 4,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 5,62</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-4,0; 3,7</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 4,36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 5,62</t>
+          <t>-6,33; 5,63</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,55; 34,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,14; 40,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,92; 46,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 33,64</t>
+          <t>-25,55; 34,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 39,38</t>
+          <t>-23,14; 40,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 46,85</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-26,42; 33,64</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-24,99; 39,38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-44,37; 46,85</t>
+          <t>-42,92; 46,23</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>0,03</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,36; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,94; 5,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,49; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,31</t>
+          <t>-6,36; 4,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,99</t>
+          <t>-4,94; 5,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 4,31</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-4,88; 5,99</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-5,59; 5,27</t>
+          <t>-5,49; 5,72</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-1,92%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-1,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,26; 13,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,27; 17,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,21; 17,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 13,87</t>
+          <t>-17,26; 13,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 19,39</t>
+          <t>-13,27; 17,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 17,02</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-16,89; 13,87</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-13,33; 19,39</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-15,87; 17,02</t>
+          <t>-15,21; 17,7</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4,16</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2,74</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,77; 10,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,62; 9,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,13; 10,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 10,21</t>
+          <t>-0,77; 10,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 10,38</t>
+          <t>-1,62; 9,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 11,29</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-1,5; 10,21</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 10,38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-3,05; 11,29</t>
+          <t>-3,13; 10,89</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4,43%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,14; 18,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,35; 17,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,92; 18,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 17,38</t>
+          <t>-1,14; 18,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 17,77</t>
+          <t>-2,35; 17,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 19,19</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 17,38</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 17,77</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 19,19</t>
+          <t>-4,92; 18,66</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,89</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,69</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,89</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14,7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4,69</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,77; 20,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,43; 20,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,73; 9,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,29; 21,19</t>
+          <t>10,77; 20,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 19,92</t>
+          <t>9,43; 20,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 9,97</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 21,19</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>9,65; 19,92</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 9,97</t>
+          <t>-0,73; 9,73</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,65; 29,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,72; 28,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,85; 13,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,66; 29,64</t>
+          <t>13,65; 29,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,43; 27,77</t>
+          <t>11,72; 28,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,79</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>14,66; 29,64</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>12,43; 27,77</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 13,79</t>
+          <t>-0,85; 13,51</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21,88</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,58</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27,03</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>27,03</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>21,88</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>22,58</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>27,03</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,82; 27,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,44; 28,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,26; 37,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15,01; 27,86</t>
+          <t>15,82; 27,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,73; 28,83</t>
+          <t>16,44; 28,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,1; 37,56</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,01; 27,86</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16,73; 28,83</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>19,1; 37,56</t>
+          <t>19,26; 37,14</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>35,59%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>42,62%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,88; 47,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,45; 48,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,67; 63,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22,61; 47,74</t>
+          <t>23,88; 47,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,3; 48,44</t>
+          <t>24,45; 48,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,03; 65,84</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>22,61; 47,74</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>24,3; 48,44</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>29,03; 65,84</t>
+          <t>29,67; 63,04</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24,75</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30,92</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41,34</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>41,34</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>24,75</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>30,92</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>41,34</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,92; 32,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,45; 38,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,95; 47,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17,57; 32,75</t>
+          <t>17,92; 32,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,4; 39,55</t>
+          <t>23,45; 38,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,32; 47,34</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,57; 32,75</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>23,4; 39,55</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>35,32; 47,34</t>
+          <t>34,95; 47,4</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>106,45%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>142,31%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>142,31%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>85,21%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>106,45%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>142,31%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,57; 128,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>70,37; 158,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>102,35; 196,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54,59; 131,92</t>
+          <t>53,57; 128,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>72,58; 160,72</t>
+          <t>70,37; 158,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>106,04; 196,52</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>54,59; 131,92</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>72,58; 160,72</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>106,04; 196,52</t>
+          <t>102,35; 196,6</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,02</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>18,02</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,59</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,29</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,12; 28,66</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>6,75; 11,59</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 14,29</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>13,12; 28,66</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>47,53%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,24; 31,67</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,03</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,13; 77,23</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>17,24; 31,67</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>23,98; 39,03</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>34,13; 77,23</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
     </row>
@@ -2347,14 +1839,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43-Edad-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,51</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,97</t>
+          <t>-2,52; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,03</t>
+          <t>-3,29; 2,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,2</t>
+          <t>-2,01; 7,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,97</t>
+          <t>-2,52; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,03</t>
+          <t>-3,29; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,2</t>
+          <t>-2,01; 7,33</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 91,14</t>
+          <t>-38,11; 81,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 69,78</t>
+          <t>-45,5; 63,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 175,53</t>
+          <t>-32,08; 150,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 91,14</t>
+          <t>-38,11; 81,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 69,78</t>
+          <t>-45,5; 63,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 175,53</t>
+          <t>-32,08; 150,15</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,85</t>
+          <t>-3,78; 3,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,25</t>
+          <t>-3,35; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 5,63</t>
+          <t>-3,3; 5,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,85</t>
+          <t>-3,78; 3,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,25</t>
+          <t>-3,35; 4,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 5,63</t>
+          <t>-3,3; 5,99</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 34,72</t>
+          <t>-24,59; 36,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 40,26</t>
+          <t>-22,77; 38,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 46,23</t>
+          <t>-21,8; 51,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 34,72</t>
+          <t>-24,59; 36,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 40,26</t>
+          <t>-22,77; 38,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 46,23</t>
+          <t>-21,8; 51,47</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,57</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,27</t>
+          <t>-5,95; 5,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,4</t>
+          <t>-5,02; 5,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 5,72</t>
+          <t>-5,99; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,27</t>
+          <t>-5,95; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,4</t>
+          <t>-5,02; 5,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 5,72</t>
+          <t>-5,99; 4,2</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>-1,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>-1,69%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 13,54</t>
+          <t>-16,2; 16,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 17,48</t>
+          <t>-13,58; 16,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 17,7</t>
+          <t>-16,41; 13,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 13,54</t>
+          <t>-16,2; 16,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 17,48</t>
+          <t>-13,58; 16,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 17,7</t>
+          <t>-16,41; 13,6</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,81</t>
+          <t>-1,02; 10,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 9,76</t>
+          <t>-1,51; 9,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,89</t>
+          <t>-6,08; 5,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,81</t>
+          <t>-1,02; 10,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 9,76</t>
+          <t>-1,51; 9,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,89</t>
+          <t>-6,08; 5,38</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>-0,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>-0,18%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 18,7</t>
+          <t>-1,61; 19,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 17,03</t>
+          <t>-2,28; 16,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 18,66</t>
+          <t>-9,33; 9,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 18,7</t>
+          <t>-1,61; 19,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 17,03</t>
+          <t>-2,28; 16,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 18,66</t>
+          <t>-9,33; 9,25</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>3,99</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,85</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,53</t>
+          <t>9,15; 19,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,73</t>
+          <t>-1,08; 9,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,85</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,53</t>
+          <t>9,15; 19,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,73</t>
+          <t>-1,08; 9,35</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13,65; 29,22</t>
+          <t>13,32; 29,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,72; 28,46</t>
+          <t>11,88; 27,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 13,51</t>
+          <t>-1,39; 12,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,65; 29,22</t>
+          <t>13,32; 29,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,72; 28,46</t>
+          <t>11,88; 27,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 13,51</t>
+          <t>-1,39; 12,85</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27,03</t>
+          <t>21,66</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,03</t>
+          <t>21,66</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>15,82; 27,84</t>
+          <t>15,17; 27,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16,44; 28,69</t>
+          <t>16,31; 28,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19,26; 37,14</t>
+          <t>15,47; 27,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15,82; 27,84</t>
+          <t>15,17; 27,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,44; 28,69</t>
+          <t>16,31; 28,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,26; 37,14</t>
+          <t>15,47; 27,15</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23,88; 47,48</t>
+          <t>22,31; 46,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24,45; 48,02</t>
+          <t>24,25; 48,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29,67; 63,04</t>
+          <t>22,69; 45,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23,88; 47,48</t>
+          <t>22,31; 46,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,45; 48,02</t>
+          <t>24,25; 48,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,67; 63,04</t>
+          <t>22,69; 45,99</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41,34</t>
+          <t>41,17</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,34</t>
+          <t>41,17</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>17,92; 32,04</t>
+          <t>17,01; 31,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23,45; 38,95</t>
+          <t>22,87; 38,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34,95; 47,4</t>
+          <t>34,37; 46,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17,92; 32,04</t>
+          <t>17,01; 31,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,45; 38,95</t>
+          <t>22,87; 38,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,95; 47,4</t>
+          <t>34,37; 46,96</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142,31%</t>
+          <t>141,71%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>142,31%</t>
+          <t>141,71%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>53,57; 128,19</t>
+          <t>51,15; 127,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>70,37; 158,02</t>
+          <t>69,86; 161,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>102,35; 196,6</t>
+          <t>99,83; 190,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53,57; 128,19</t>
+          <t>51,15; 127,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>70,37; 158,02</t>
+          <t>69,86; 161,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>102,35; 196,6</t>
+          <t>99,83; 190,78</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
     </row>
